--- a/data/trans_orig/P80_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P80_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>388130</t>
+          <t>391780</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>371129</t>
+          <t>373617</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>396627</t>
+          <t>401392</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>301213</t>
+          <t>349483</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>290819</t>
+          <t>337288</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>307454</t>
+          <t>356282</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>689343</t>
+          <t>741263</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>670584</t>
+          <t>722746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>701354</t>
+          <t>753756</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>11783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29203</t>
+          <t>31335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16190</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>24274</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8546</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>408070</t>
+          <t>457536</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>395751</t>
+          <t>443428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>415670</t>
+          <t>466383</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>502165</t>
+          <t>491584</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>493041</t>
+          <t>484342</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>507083</t>
+          <t>496137</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>910236</t>
+          <t>949121</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>894892</t>
+          <t>933972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>919724</t>
+          <t>959869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>17776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13648</t>
+          <t>18875</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>15009</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>510457</t>
+          <t>500023</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>510457</t>
+          <t>500023</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>510457</t>
+          <t>500023</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>934005</t>
+          <t>976914</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>934005</t>
+          <t>976914</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>934005</t>
+          <t>976914</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>519474</t>
+          <t>601605</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>509522</t>
+          <t>590278</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>526654</t>
+          <t>609558</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>533362</t>
+          <t>611412</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>527212</t>
+          <t>604846</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>537514</t>
+          <t>615949</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1052836</t>
+          <t>1213017</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1042397</t>
+          <t>1200134</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1061530</t>
+          <t>1222320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,22 +2272,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>25436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,67 +2350,67 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>1596</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>10724</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>0,13%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3415</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,22 +2611,22 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>872615</t>
+          <t>682397</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>861033</t>
+          <t>673287</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>880966</t>
+          <t>688934</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>698993</t>
+          <t>720183</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>693045</t>
+          <t>712734</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>703070</t>
+          <t>724810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1571608</t>
+          <t>1402580</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1560476</t>
+          <t>1390956</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1582322</t>
+          <t>1410853</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>19054</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>14558</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>23909</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>13297</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,17 +3145,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>914</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>862</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>886104</t>
+          <t>698763</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>886104</t>
+          <t>698763</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>886104</t>
+          <t>698763</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>709661</t>
+          <t>733264</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>709661</t>
+          <t>733264</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>709661</t>
+          <t>733264</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1595765</t>
+          <t>1432027</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1595765</t>
+          <t>1432027</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1595765</t>
+          <t>1432027</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>554264</t>
+          <t>602009</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>548624</t>
+          <t>596233</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>557847</t>
+          <t>605746</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>541802</t>
+          <t>602209</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>536989</t>
+          <t>596397</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>544701</t>
+          <t>605080</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1096066</t>
+          <t>1204218</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1089517</t>
+          <t>1197048</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1101191</t>
+          <t>1209220</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -3566,102 +3566,102 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>821</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5345</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>4640</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>9880</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>4532</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>1845</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>9562</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,22 +3714,22 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>560303</t>
+          <t>608357</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>560303</t>
+          <t>608357</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>560303</t>
+          <t>608357</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>547274</t>
+          <t>608166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>547274</t>
+          <t>608166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>547274</t>
+          <t>608166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1107577</t>
+          <t>1216523</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1107577</t>
+          <t>1216523</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1107577</t>
+          <t>1216523</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>366477</t>
+          <t>405321</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>363532</t>
+          <t>401992</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>367651</t>
+          <t>406578</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>603792</t>
+          <t>434099</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>600570</t>
+          <t>430580</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>605911</t>
+          <t>435837</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>970268</t>
+          <t>839419</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>966392</t>
+          <t>834968</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>973135</t>
+          <t>841804</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>697</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>560</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>793</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>362</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>502</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>502</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4667,12 +4667,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>606294</t>
+          <t>436814</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>606294</t>
+          <t>436814</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>606294</t>
+          <t>436814</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>974459</t>
+          <t>843893</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>974459</t>
+          <t>843893</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>974459</t>
+          <t>843893</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4852,27 +4852,27 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>424145</t>
+          <t>462835</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>421004</t>
+          <t>460029</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4887,27 +4887,27 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>706904</t>
+          <t>773033</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>704402</t>
+          <t>770051</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>616</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>616</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>562</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>562</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3391790</t>
+          <t>3450847</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3368649</t>
+          <t>3424953</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3412246</t>
+          <t>3469150</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>3605471</t>
+          <t>3671806</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3591344</t>
+          <t>3656141</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3618615</t>
+          <t>3683414</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>6997261</t>
+          <t>7122653</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>6970720</t>
+          <t>7092094</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7020570</t>
+          <t>7146288</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>37190</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>28895</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>57305</t>
+          <t>63289</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>18810</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>54053</t>
+          <t>61038</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>39076</t>
+          <t>46894</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>73596</t>
+          <t>80997</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>29751</t>
+          <t>38891</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>14411</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>23671</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>31866</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>27062</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>47070</t>
+          <t>56183</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,17 +5873,17 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>10711</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>20261</t>
+          <t>24670</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>23324</t>
+          <t>24471</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>28699</t>
+          <t>31508</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
